--- a/examples/demo_算法推荐短视频侵权/output/短视频侵权案件-类案检索清单-20260607.xlsx
+++ b/examples/demo_算法推荐短视频侵权/output/短视频侵权案件-类案检索清单-20260607.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="案件清单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权威案例附录" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="裁判分歧清单" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'案件清单'!$A$1:$AC$7</definedName>
@@ -1555,4 +1556,142 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>争议焦点</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>立场A(件数)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>立场A代表案号</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>立场B(件数)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>立场B代表案号</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>其他立场</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>样本提示</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>平台是否构成信息网络传播权侵权</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>支持原告（5）</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>（2021）示01民初0001号；（2022）示01民初0042号</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>支持被告（1）</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>（2023）示73民初0256号</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>对立观点并存（个案观点分布；分组样本不足，不构成地域/层级倾向结论）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>“通知—必要措施”义务是否履行到位</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>支持原告（5）</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>（2021）示01民初0001号；（2022）示01民初0042号</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>支持被告（1）</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>（2023）示73民初0256号</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>对立观点并存（个案观点分布；分组样本不足，不构成地域/层级倾向结论）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>